--- a/muestreo/analytica/Report/Lote-Export-Muestreo-Base.xlsx
+++ b/muestreo/analytica/Report/Lote-Export-Muestreo-Base.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\muestreo\analytica\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E4CD91-CCAB-4A9B-A45A-04A0610B0B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A5A3D6-36BC-4337-B985-7F303BB3F1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,7 +90,7 @@
     <t>MUESTREADO</t>
   </si>
   <si>
-    <t>ESTADOI MUESTREO</t>
+    <t>ESTADO MUESTREO</t>
   </si>
 </sst>
 </file>
@@ -101,7 +101,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-&quot;S/ &quot;* #,##0.00_-;&quot;-S/ &quot;* #,##0.00_-;_-&quot;S/ &quot;* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +165,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -230,7 +238,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -272,11 +280,26 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="24">
@@ -568,13 +591,14 @@
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" customWidth="1"/>
     <col min="3" max="3" width="23.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="61.109375" style="18" customWidth="1"/>
     <col min="5" max="5" width="23.88671875" customWidth="1"/>
     <col min="6" max="6" width="28.44140625" customWidth="1"/>
     <col min="7" max="7" width="25.77734375" customWidth="1"/>
     <col min="8" max="8" width="28.5546875" customWidth="1"/>
     <col min="9" max="9" width="24.77734375" customWidth="1"/>
-    <col min="10" max="17" width="14.88671875" customWidth="1"/>
+    <col min="10" max="16" width="14.88671875" customWidth="1"/>
+    <col min="17" max="17" width="27.77734375" customWidth="1"/>
     <col min="18" max="18" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -582,7 +606,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -639,17 +663,17 @@
       <c r="BF1" s="3"/>
     </row>
     <row r="2" spans="1:58" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -701,17 +725,17 @@
       <c r="BF2" s="3"/>
     </row>
     <row r="3" spans="1:58" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -766,7 +790,7 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="D4" s="16"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -826,7 +850,7 @@
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+      <c r="D5" s="17"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
@@ -847,8 +871,8 @@
       <c r="B6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="6"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="9" t="s">
@@ -861,7 +885,7 @@
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
+      <c r="D7" s="10"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -877,7 +901,7 @@
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:58" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>4</v>
       </c>
@@ -930,7 +954,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:58" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:58" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="18"/>
+    </row>
     <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="F11" t="s">
         <v>8</v>

--- a/muestreo/analytica/Report/Lote-Export-Muestreo-Base.xlsx
+++ b/muestreo/analytica/Report/Lote-Export-Muestreo-Base.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\muestreo\analytica\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A5A3D6-36BC-4337-B985-7F303BB3F1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BBBC64-C65F-4809-A499-423A1841F855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -63,12 +63,6 @@
     <t>TIPO MINERAL</t>
   </si>
   <si>
-    <t>CONDICION CHANCADO</t>
-  </si>
-  <si>
-    <t>FECHA MUESTREO</t>
-  </si>
-  <si>
     <t>OPERADOR</t>
   </si>
   <si>
@@ -90,7 +84,13 @@
     <t>MUESTREADO</t>
   </si>
   <si>
-    <t>ESTADO MUESTREO</t>
+    <t>CONDICION UBICACIÓN EN CANCHA</t>
+  </si>
+  <si>
+    <t>FECHA CERTIFICADO DE HUMEDAD</t>
+  </si>
+  <si>
+    <t>ESTADO CERTIFICADO DE HUMEDAD</t>
   </si>
 </sst>
 </file>
@@ -292,14 +292,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="24">
@@ -663,17 +663,17 @@
       <c r="BF1" s="3"/>
     </row>
     <row r="2" spans="1:58" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -725,17 +725,17 @@
       <c r="BF2" s="3"/>
     </row>
     <row r="3" spans="1:58" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -871,7 +871,7 @@
       <c r="B6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="21"/>
+      <c r="C6" s="19"/>
       <c r="D6" s="10"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -901,7 +901,7 @@
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:58" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>4</v>
       </c>
@@ -924,31 +924,31 @@
         <v>6</v>
       </c>
       <c r="H8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="K8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="L8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="M8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="N8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="O8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="N8" s="12" t="s">
+      <c r="P8" s="12" t="s">
         <v>18</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>20</v>
       </c>
       <c r="Q8" s="12" t="s">
         <v>21</v>

--- a/muestreo/analytica/Report/Lote-Export-Muestreo-Base.xlsx
+++ b/muestreo/analytica/Report/Lote-Export-Muestreo-Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\muestreo\analytica\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BBBC64-C65F-4809-A499-423A1841F855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E82C40F-156F-4249-AEDF-EE993B5DADBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Analytica Mineral Services Sac</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>ESTADO CERTIFICADO DE HUMEDAD</t>
+  </si>
+  <si>
+    <t>CERTIFICADO DE HUMEDAD</t>
   </si>
 </sst>
 </file>
@@ -585,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BF11"/>
+  <dimension ref="A1:BG11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
@@ -597,12 +600,12 @@
     <col min="7" max="7" width="25.77734375" customWidth="1"/>
     <col min="8" max="8" width="28.5546875" customWidth="1"/>
     <col min="9" max="9" width="24.77734375" customWidth="1"/>
-    <col min="10" max="16" width="14.88671875" customWidth="1"/>
-    <col min="17" max="17" width="27.77734375" customWidth="1"/>
-    <col min="18" max="18" width="17.33203125" customWidth="1"/>
+    <col min="10" max="17" width="14.88671875" customWidth="1"/>
+    <col min="18" max="18" width="27.77734375" customWidth="1"/>
+    <col min="19" max="19" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -661,8 +664,9 @@
       <c r="BD1" s="3"/>
       <c r="BE1" s="3"/>
       <c r="BF1" s="3"/>
+      <c r="BG1" s="3"/>
     </row>
-    <row r="2" spans="1:58" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:59" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
@@ -682,8 +686,8 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="3"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="4"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
@@ -723,8 +727,9 @@
       <c r="BD2" s="3"/>
       <c r="BE2" s="3"/>
       <c r="BF2" s="3"/>
+      <c r="BG2" s="3"/>
     </row>
-    <row r="3" spans="1:58" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:59" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
@@ -744,8 +749,8 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="3"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="5"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
@@ -785,8 +790,9 @@
       <c r="BD3" s="3"/>
       <c r="BE3" s="3"/>
       <c r="BF3" s="3"/>
+      <c r="BG3" s="3"/>
     </row>
-    <row r="4" spans="1:58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:59" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -804,7 +810,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
-      <c r="R4" s="3"/>
+      <c r="R4" s="4"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -845,8 +851,9 @@
       <c r="BD4" s="3"/>
       <c r="BE4" s="3"/>
       <c r="BF4" s="3"/>
+      <c r="BG4" s="3"/>
     </row>
-    <row r="5" spans="1:58" ht="18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:59" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -864,9 +871,10 @@
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
-      <c r="R5" s="6"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="6"/>
     </row>
-    <row r="6" spans="1:58" ht="18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:59" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="9" t="s">
         <v>2</v>
@@ -879,9 +887,9 @@
         <v>3</v>
       </c>
       <c r="H6" s="11"/>
-      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
     </row>
-    <row r="7" spans="1:58" ht="18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:59" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -900,8 +908,9 @@
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
     </row>
-    <row r="8" spans="1:58" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:59" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>4</v>
       </c>
@@ -951,13 +960,16 @@
         <v>18</v>
       </c>
       <c r="Q8" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R8" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:58" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:59" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D9" s="18"/>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:59" x14ac:dyDescent="0.3">
       <c r="F11" t="s">
         <v>8</v>
       </c>
